--- a/config/new-five-tables/source/04_TCIM_十题_开放探询可供性与稀疏监督表_V0.2.1_唯一运行版.xlsx
+++ b/config/new-five-tables/source/04_TCIM_十题_开放探询可供性与稀疏监督表_V0.2.1_唯一运行版.xlsx
@@ -2,14 +2,14 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="README" sheetId="1" r:id="R8c51d56abc684450"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="RUNTIME_CONTRACT" sheetId="2" r:id="R34a5756924ab4c94"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="QUESTION_INDEX" sheetId="3" r:id="Rf8b9d7d4f0274581"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="DATA" sheetId="4" r:id="Rf9a62a3d76bc4c9e"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="DICTIONARY" sheetId="5" r:id="Rb9d5747f7b0746ad"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="ENUMS" sheetId="6" r:id="Rd8fe777564d54926"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="QA_SUMMARY" sheetId="7" r:id="R6b23deb3cdf247df"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="CHANGELOG" sheetId="8" r:id="R78583fe8a6f94de3"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="README" sheetId="1" r:id="R71cc62b2e52c4ab1"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="RUNTIME_CONTRACT" sheetId="2" r:id="R7020fcdc6b78404d"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="QUESTION_INDEX" sheetId="3" r:id="R5a0d28267bf54253"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="DATA" sheetId="4" r:id="R66f559187b0a4505"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="DICTIONARY" sheetId="5" r:id="R31ccb1bf9b1046ac"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="ENUMS" sheetId="6" r:id="Rd502f13395704330"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="QA_SUMMARY" sheetId="7" r:id="R418c46bb655148b4"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="CHANGELOG" sheetId="8" r:id="Rcb14eba3a47b456f"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -9338,7 +9338,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R4fb95a402d59456e"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R0604807670a645bb"/>
   </x:tableParts>
 </x:worksheet>
 </file>
